--- a/docs/EAA_Backlog_Tien_hoa.xlsx
+++ b/docs/EAA_Backlog_Tien_hoa.xlsx
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
@@ -2862,17 +2862,17 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>eaa/cli.py · eaa/jsonout.py (mới)</t>
+          <t>eaa/cli.py · eaa/jsonout.py</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>Số lệnh chỉ đọc có `--json`, trên tổng số lệnh chỉ đọc</t>
+          <t>ĐÃ ĐO: 5/36 lệnh chỉ đọc có `--json` (status · policy · packs · procedure · gate show). Phần còn lại là việc CHƯA LÀM, không phải đã bỏ</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>cần TC mới — canh cả việc lệnh GHI không có `--json`</t>
+          <t>TC-148 (15 bài, 6 đột biến đều bị bắt) — canh cả việc lệnh GHI không có `--json`</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
@@ -2900,9 +2900,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="P23" s="17" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="P23" s="19" t="inlineStr">
+        <is>
+          <t>CƠ CHẾ XONG — 5/36 lệnh</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Số lệnh chỉ đọc có `--json`, trên tổng số lệnh chỉ đọc</t>
+          <t>ĐÃ ĐO: 5/36 lệnh chỉ đọc có `--json` (status · policy · packs · procedure · gate show). Phần còn lại là việc CHƯA LÀM, không phải đã bỏ</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>CHƯA</t>
+          <t>CƠ CHẾ XONG — 5/36 lệnh</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6454,15 +6454,59 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>CƠ CHẾ XONG — SL-182, TC-148</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>5/36 lệnh chỉ đọc có --json. Làm lộ một lỗi thật của SL-178: phép rút tên lệnh nhặt nhầm giá trị của --project, nên câu 'làm tiếp' mất trong im lặng</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>D8 · SC-28</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>SỬA — bản đầu mô tả một lệnh ĐÃ CÓ</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>`eaa sim run/sweep` vốn đã tồn tại; sở cứ SC-28 được gán hạng ĐO trong khi chưa hề được đo. Xem SL-183</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
           <t>toàn bảng</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>THIẾT KẾ LẠI thành backlog tiến hoá</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>14 việc → 32 việc, chia sáu mảng. Mảng D (mô phỏng) và E (IDE) dựng mới sau khi rà soát: kho đã có MiL + SIL chạy firmware thật, còn IDE bị chặn ở chỗ CLI chưa có đầu ra máy đọc được</t>
         </is>

--- a/docs/EAA_Backlog_Tien_hoa.xlsx
+++ b/docs/EAA_Backlog_Tien_hoa.xlsx
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
@@ -2939,22 +2939,22 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>1) `ToolError` đã mang sẵn `file`, `line`, `rule_id`, `severity` — việc này gần như chỉ là xuất ra. 2) `eaa verify --json` trả danh sách chẩn đoán. 3) Lỗi KHÔNG có vị trí vẫn phải xuất, gắn vào tệp dự án — nuốt chúng đi là giấu đúng những lỗi khó nhất.</t>
+          <t>1) KHÔNG có lệnh nào chạy lại cổng mà chỉ đọc — `eaa verify` mà bản đầu của việc này nhắc tới không tồn tại (SL-184). Nên đọc thứ ĐÃ CẤT. 2) Ba nguồn: bằng chứng cổng, lý do NGƯỜI từ chối gate, và sổ lỗi. 3) Lỗi KHÔNG có vị trí vẫn phải xuất — 8/13 lần từ chối là lỗi thiết kế không có vị trí nào. 4) Tách LỊCH SỬ đã khép khỏi cái đang mở.</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>eaa/cli.py · eaa/tools/base.py</t>
+          <t>eaa/diagnostic.py · eaa/cli.py `cmd_problems`</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>Phần trăm lỗi cổng có `file`+`line` dùng được để vẽ gạch đỏ</t>
+          <t>ĐÃ ĐO trên dự án thật: 87 phát hiện · 65 lịch sử · 22 đang mở · 1/22 (5%) vẽ được gạch đỏ</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>cần TC mới</t>
+          <t>TC-149 (19 bài, 6 đột biến đều bị bắt)</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -2982,9 +2982,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="P24" s="17" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="P24" s="19" t="inlineStr">
+        <is>
+          <t>CƠ CHẾ XONG — 1/22 có vị trí</t>
         </is>
       </c>
     </row>
@@ -4190,12 +4190,12 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>1) `ToolError` đã mang sẵn `file`, `line`, `rule_id`, `severity` — việc này gần như chỉ là xuất ra. 2) `eaa verify --json` trả danh sách chẩn đoán. 3) Lỗi KHÔNG có vị trí vẫn phải xuất, gắn vào tệp dự án — nuốt chúng đi là giấu đúng những lỗi khó nhất.</t>
+          <t>1) KHÔNG có lệnh nào chạy lại cổng mà chỉ đọc — `eaa verify` mà bản đầu của việc này nhắc tới không tồn tại (SL-184). Nên đọc thứ ĐÃ CẤT. 2) Ba nguồn: bằng chứng cổng, lý do NGƯỜI từ chối gate, và sổ lỗi. 3) Lỗi KHÔNG có vị trí vẫn phải xuất — 8/13 lần từ chối là lỗi thiết kế không có vị trí nào. 4) Tách LỊCH SỬ đã khép khỏi cái đang mở.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Phần trăm lỗi cổng có `file`+`line` dùng được để vẽ gạch đỏ</t>
+          <t>ĐÃ ĐO trên dự án thật: 87 phát hiện · 65 lịch sử · 22 đang mở · 1/22 (5%) vẽ được gạch đỏ</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -4919,12 +4919,12 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>`ToolError` đã mang sẵn `file`, `line`, `rule_id`, `severity` — đủ cho một chẩn đoán trong biên tập. Chỉ thiếu chỗ xuất ra</t>
+          <t>`ToolError` mang sẵn `file`/`line`/`rule_id`/`severity`, và hồ sơ trong `.eaa/runs/` giữ nguyên cả bốn qua vòng ghi–đọc. NHƯNG hồ sơ chỉ được cất khi mã ĐÃ ĐẠT — lỗi có vị trí của lượt trượt chỉ còn trong `error_ledger.jsonl`, dạng văn xuôi</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>eaa/tools/base.py:40-59</t>
+          <t>eaa/tools/base.py:40-59 · eaa/orchestrator.py:463 · eaa problems</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>CHƯA</t>
+          <t>CƠ CHẾ XONG — 1/22 có vị trí</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6454,17 +6454,17 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>CƠ CHẾ XONG — SL-182, TC-148</t>
+          <t>CƠ CHẾ XONG — SL-184, TC-149</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>5/36 lệnh chỉ đọc có --json. Làm lộ một lỗi thật của SL-178: phép rút tên lệnh nhặt nhầm giá trị của --project, nên câu 'làm tiếp' mất trong im lặng</t>
+          <t>`eaa problems`. Đo được 87 phát hiện · 65 lịch sử · 22 đang mở · 1/22 có vị trí. Bản đầu bày cả 66 mục sổ lỗi như lỗi hiện tại — sổ ấy là append-only nên phần lớn đã sửa xong</t>
         </is>
       </c>
     </row>
@@ -6476,17 +6476,17 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>D8 · SC-28</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>SỬA — bản đầu mô tả một lệnh ĐÃ CÓ</t>
+          <t>CƠ CHẾ XONG — SL-182, TC-148</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>`eaa sim run/sweep` vốn đã tồn tại; sở cứ SC-28 được gán hạng ĐO trong khi chưa hề được đo. Xem SL-183</t>
+          <t>5/36 lệnh chỉ đọc có --json. Làm lộ một lỗi thật của SL-178: phép rút tên lệnh nhặt nhầm giá trị của --project, nên câu 'làm tiếp' mất trong im lặng</t>
         </is>
       </c>
     </row>
@@ -6498,15 +6498,37 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
+          <t>D8 · SC-28</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>SỬA — bản đầu mô tả một lệnh ĐÃ CÓ</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>`eaa sim run/sweep` vốn đã tồn tại; sở cứ SC-28 được gán hạng ĐO trong khi chưa hề được đo. Xem SL-183</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
           <t>toàn bảng</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>THIẾT KẾ LẠI thành backlog tiến hoá</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>14 việc → 32 việc, chia sáu mảng. Mảng D (mô phỏng) và E (IDE) dựng mới sau khi rà soát: kho đã có MiL + SIL chạy firmware thật, còn IDE bị chặn ở chỗ CLI chưa có đầu ra máy đọc được</t>
         </is>

--- a/docs/EAA_Backlog_Tien_hoa.xlsx
+++ b/docs/EAA_Backlog_Tien_hoa.xlsx
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
@@ -3021,22 +3021,22 @@
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>1) Hiện 5 gate, gate nào đang chờ, lý do từ chối gần nhất. 2) Bấm duyệt trong IDE vẫn gọi ĐÚNG `eaa gate approve` với cùng dấu vân tay nội dung — không có API riêng, không có đường vòng. 3) IDE không được tự bấm bất cứ gate nào.</t>
+          <t>1) `eaa gate show --json` trả 5 gate kèm mục đích, trạng thái và QUYẾT ĐỊNH GẦN NHẤT (người, lúc nào, lý do nguyên văn nếu từ chối). 2) Ghi lại việc người duyệt có khẳng định dấu vân tay không, ở BA trạng thái. 3) Cưỡng chế qua công tắc `EAA_REQUIRE_GATE_DIGEST`, mặc định TẮT — bật nó là quyết định về sản phẩm, đụng 31 chỗ gọi trong bộ kiểm. 4) Bài canh cấu trúc: không chỗ nào ngoài `eaa/gates.py` dựng ra quyết định DUYỆT.</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>tích hợp riêng · eaa/cli.py (chỉ đọc)</t>
+          <t>eaa/gates.py · eaa/cli.py `_bang_gate` · `_duyet_mu`</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>Số bước từ mở dự án tới thấy 'đang mắc ở gate nào'</t>
+          <t>ĐÃ ĐO: MỘT lệnh (`eaa gate show --json`) đủ biết đang mắc ở gate nào. 38 quyết định cũ đều ở hạng KHÔNG KIỂM ĐƯỢC, không bị khai thành duyệt mù</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>TC-01, TC-02 đã canh bất biến; cần TC cho lớp mỏng</t>
+          <t>TC-150 (15 bài, 8 đột biến — 1 phép hỏng, 1 phép làm lộ bài kiểm rỗng)</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
@@ -3064,9 +3064,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="P25" s="17" t="inlineStr">
-        <is>
-          <t>CHƯA</t>
+      <c r="P25" s="19" t="inlineStr">
+        <is>
+          <t>CƠ CHẾ XONG — công tắc mặc định tắt</t>
         </is>
       </c>
     </row>
@@ -4222,12 +4222,12 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1) Hiện 5 gate, gate nào đang chờ, lý do từ chối gần nhất. 2) Bấm duyệt trong IDE vẫn gọi ĐÚNG `eaa gate approve` với cùng dấu vân tay nội dung — không có API riêng, không có đường vòng. 3) IDE không được tự bấm bất cứ gate nào.</t>
+          <t>1) `eaa gate show --json` trả 5 gate kèm mục đích, trạng thái và QUYẾT ĐỊNH GẦN NHẤT (người, lúc nào, lý do nguyên văn nếu từ chối). 2) Ghi lại việc người duyệt có khẳng định dấu vân tay không, ở BA trạng thái. 3) Cưỡng chế qua công tắc `EAA_REQUIRE_GATE_DIGEST`, mặc định TẮT — bật nó là quyết định về sản phẩm, đụng 31 chỗ gọi trong bộ kiểm. 4) Bài canh cấu trúc: không chỗ nào ngoài `eaa/gates.py` dựng ra quyết định DUYỆT.</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Số bước từ mở dự án tới thấy 'đang mắc ở gate nào'</t>
+          <t>ĐÃ ĐO: MỘT lệnh (`eaa gate show --json`) đủ biết đang mắc ở gate nào. 38 quyết định cũ đều ở hạng KHÔNG KIỂM ĐƯỢC, không bị khai thành duyệt mù</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>CHƯA</t>
+          <t>CƠ CHẾ XONG — công tắc mặc định tắt</t>
         </is>
       </c>
     </row>
@@ -6283,7 +6283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6454,17 +6454,17 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>CƠ CHẾ XONG — SL-184, TC-149</t>
+          <t>CƠ CHẾ XONG — SL-185, TC-150</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>`eaa problems`. Đo được 87 phát hiện · 65 lịch sử · 22 đang mở · 1/22 có vị trí. Bản đầu bày cả 66 mục sổ lỗi như lỗi hiện tại — sổ ấy là append-only nên phần lớn đã sửa xong</t>
+          <t>Bảng gate trong một lệnh. Tìm ra chỗ hở thật: --expect là tuỳ chọn nên một nút bấm duyệt được thứ chưa từng cho ai xem. Cưỡng chế đặt sau một công tắc mặc định TẮT — bật nó là quyết định của người chủ dự án</t>
         </is>
       </c>
     </row>
@@ -6476,17 +6476,17 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>CƠ CHẾ XONG — SL-182, TC-148</t>
+          <t>CƠ CHẾ XONG — SL-184, TC-149</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>5/36 lệnh chỉ đọc có --json. Làm lộ một lỗi thật của SL-178: phép rút tên lệnh nhặt nhầm giá trị của --project, nên câu 'làm tiếp' mất trong im lặng</t>
+          <t>`eaa problems`. Đo được 87 phát hiện · 65 lịch sử · 22 đang mở · 1/22 có vị trí. Bản đầu bày cả 66 mục sổ lỗi như lỗi hiện tại — sổ ấy là append-only nên phần lớn đã sửa xong</t>
         </is>
       </c>
     </row>
@@ -6498,17 +6498,17 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>D8 · SC-28</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>SỬA — bản đầu mô tả một lệnh ĐÃ CÓ</t>
+          <t>CƠ CHẾ XONG — SL-182, TC-148</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>`eaa sim run/sweep` vốn đã tồn tại; sở cứ SC-28 được gán hạng ĐO trong khi chưa hề được đo. Xem SL-183</t>
+          <t>5/36 lệnh chỉ đọc có --json. Làm lộ một lỗi thật của SL-178: phép rút tên lệnh nhặt nhầm giá trị của --project, nên câu 'làm tiếp' mất trong im lặng</t>
         </is>
       </c>
     </row>
@@ -6520,15 +6520,37 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
+          <t>D8 · SC-28</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>SỬA — bản đầu mô tả một lệnh ĐÃ CÓ</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>`eaa sim run/sweep` vốn đã tồn tại; sở cứ SC-28 được gán hạng ĐO trong khi chưa hề được đo. Xem SL-183</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
           <t>toàn bảng</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>THIẾT KẾ LẠI thành backlog tiến hoá</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>14 việc → 32 việc, chia sáu mảng. Mảng D (mô phỏng) và E (IDE) dựng mới sau khi rà soát: kho đã có MiL + SIL chạy firmware thật, còn IDE bị chặn ở chỗ CLI chưa có đầu ra máy đọc được</t>
         </is>
